--- a/data/trending_integrated_20261026_11.xlsx
+++ b/data/trending_integrated_20261026_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58542424215</v>
+        <v>58589858225</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -619,23 +619,23 @@
         <v>8180</v>
       </c>
       <c r="R2" t="n">
-        <v>112000</v>
+        <v>336000</v>
       </c>
       <c r="S2" t="n">
         <v>305000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와의 협력 발표. 공매도 스퀴즈 기대감과 장기적 성장 가능성 제시.</t>
+          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와의 협력에 따른 주가 급등 전망. 공매도 상환 압박 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '밸류체인', '공매도 스퀴즈']</t>
+          <t>['AI 신약', '협력', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2150</v>
+        <v>2190</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.60%</t>
+          <t>'+12.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
         <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>53137357056</v>
+        <v>53637151002</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -711,7 +711,7 @@
         <v>749</v>
       </c>
       <c r="R3" t="n">
-        <v>-78000</v>
+        <v>89000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6040</v>
+        <v>6170</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.02%</t>
+          <t>'+12.39%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>31804858535</v>
+        <v>33381848805</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 부정적 언급과 함께, 특정 정치인의 지지율 상승에 따른 종목의 변동성 가능성 제시. 일부 긍정적 전망.</t>
+          <t>정치 테마주에 대한 부정적 전망 및 종목 하락 가능성 언급. 실제 근거보다는 개인적인 의견에 치중.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '지지율', '변동성']</t>
+          <t>['정치 테마주', '지지율', '하락']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1281000</v>
+        <v>1277000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.31%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G5" t="n">
-        <v>1515</v>
+        <v>1532</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1553794849500</v>
+        <v>1577495169000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치권에 대한 불만과 연기금 매도세 지적. AI 산업의 미래 전망에 대한 일부 긍정적 언급과 함께 현재 시장 상황에 대한 보수적 시각.</t>
+          <t>정치 상황 및 국민연금 운용에 대한 부정적 언급과 함께 주가 상승 및 하락에 대한 불확실한 전망 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI 산업', '연기금', '시장 상황']</t>
+          <t>['국민연금', '주가 전망', '정치 상황']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>213500</v>
+        <v>213000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>458</v>
       </c>
       <c r="G6" t="n">
-        <v>1339</v>
+        <v>1357</v>
       </c>
       <c r="H6" t="n">
         <v>46.11</v>
@@ -978,7 +978,7 @@
         <v>46.13</v>
       </c>
       <c r="O6" t="n">
-        <v>1144194847500</v>
+        <v>1171309064250</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈와 정부 정책에 대한 불만으로 주식 시장 전반에 대한 부정적 전망. 일부 개미 투자자들의 투매 가능성 언급.</t>
+          <t>현 정부 및 정치 상황에 대한 강한 비판과 함께 주식 시장 전반의 침체 우려 제기. 특정 정치인의 지지율 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['정부 정책', '시장 전망', '개미 투자자']</t>
+          <t>['정치 상황', '주식 시장', '침체']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58900</v>
+        <v>58800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-1.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.49</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7" t="n">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="H7" t="n">
         <v>40.39</v>
@@ -1070,7 +1070,7 @@
         <v>38.9</v>
       </c>
       <c r="O7" t="n">
-        <v>145679766600</v>
+        <v>148722957600</v>
       </c>
       <c r="P7" t="n">
         <v>67300</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대형 수주 공시 임박 및 공매도 세력에 대한 강한 경계. 외인 매수세 유입과 자사주 매입 등 긍정적 요인 부각.</t>
+          <t>외인 매수세 유입과 긍정적인 수급 동향을 바탕으로 주가 상승 기대감 표출. 중동 전쟁 등 외부 요인 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주 공시', '공매도', '외인 매수']</t>
+          <t>['외인 매수', '수급 동향', '상승 기대']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16510</v>
+        <v>16500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.90%</t>
+          <t>'-1.96%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
         <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>14526826085</v>
+        <v>14813946475</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57900</v>
+        <v>57800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.53%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G9" t="n">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>39383923000</v>
+        <v>40129902900</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 요인과 증권사 분석에 대한 불만 제기. 원전 사업의 향방과 한국 증시 전반에 대한 부정적 전망.</t>
+          <t>정부 정책 및 증시 상황에 대한 불만과 함께 종목의 하락 추세에 대한 부정적 전망. 근거 없는 비난 다수 포함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전 사업', '증권사 분석', '증시 전망']</t>
+          <t>['정부 정책', '증시 상황', '하락 추세']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14240</v>
+        <v>14210</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>13674906640</v>
+        <v>13864110755</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26900</v>
+        <v>26950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.45%</t>
+          <t>'-5.27%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>28448523425</v>
+        <v>29113004825</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3230</v>
+        <v>3185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-15.22%</t>
+          <t>'-16.40%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G12" t="n">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1524,13 +1524,13 @@
         <v>3555</v>
       </c>
       <c r="M12" t="n">
-        <v>3215</v>
+        <v>3185</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>17999567105</v>
+        <v>18432888339</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1539,14 +1539,14 @@
         <v>2500</v>
       </c>
       <c r="R12" t="n">
-        <v>173000</v>
+        <v>316000</v>
       </c>
       <c r="S12" t="n">
         <v>-86000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>지정학적 리스크(북한, 미국-이란) 부각으로 인한 급락 가능성 경고. 전쟁 관련 기대감과 부정적 전망 혼재.</t>
+          <t>국제 정세 악화 및 북한 관련 이슈로 인한 주가 급락 우려. 종목의 실질적인 가치에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '급락', '전쟁']</t>
+          <t>['국제 정세', '주가 급락', '전쟁']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261026_11.xlsx
+++ b/data/trending_integrated_20261026_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G2" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58589858225</v>
+        <v>58626686055</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2190</v>
+        <v>2185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.65%</t>
+          <t>'+12.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>53637151002</v>
+        <v>54477875373</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6170</v>
+        <v>5910</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.39%</t>
+          <t>'+7.65%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
         <v>112</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>33381848805</v>
+        <v>34729455680</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주에 대한 부정적 전망 및 종목 하락 가능성 언급. 실제 근거보다는 개인적인 의견에 치중.</t>
+          <t>정치 테마주 관련 내용으로, 실제 실체 없는 사기라는 의견과 함께 급락을 예상하는 의견이 혼재함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '지지율', '하락']</t>
+          <t>['정치 테마주', '실체', '급락']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1277000</v>
+        <v>1279000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G5" t="n">
-        <v>1532</v>
+        <v>1519</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1577495169000</v>
+        <v>1619970979000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치 상황 및 국민연금 운용에 대한 부정적 언급과 함께 주가 상승 및 하락에 대한 불확실한 전망 제시.</t>
+          <t>정치적 이슈와 연금 관련 언급이 혼재하며, 주가 부양에 대한 기대와 함께 주가 하락 가능성에 대한 우려가 나타남.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['국민연금', '주가 전망', '정치 상황']</t>
+          <t>['정치', '연금', '주가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>213000</v>
+        <v>212750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.16%</t>
+          <t>'-1.28%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G6" t="n">
-        <v>1357</v>
+        <v>1380</v>
       </c>
       <c r="H6" t="n">
         <v>46.11</v>
@@ -978,7 +978,7 @@
         <v>46.13</v>
       </c>
       <c r="O6" t="n">
-        <v>1171309064250</v>
+        <v>1212285027000</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>현 정부 및 정치 상황에 대한 강한 비판과 함께 주식 시장 전반의 침체 우려 제기. 특정 정치인의 지지율 언급.</t>
+          <t>정치 관련 부정적인 언급과 함께 한국 증시에 대한 불만이 표출되며, 주식 시장 자체에 대한 회의적인 시각을 보임.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['정치 상황', '주식 시장', '침체']</t>
+          <t>['정치', '한국 증시', '회의론']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58800</v>
+        <v>58900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.67%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.49</v>
       </c>
       <c r="E7" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F7" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="H7" t="n">
         <v>40.39</v>
@@ -1070,7 +1070,7 @@
         <v>38.9</v>
       </c>
       <c r="O7" t="n">
-        <v>148722957600</v>
+        <v>152096119950</v>
       </c>
       <c r="P7" t="n">
         <v>67300</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16500</v>
+        <v>16440</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.96%</t>
+          <t>'-2.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>14813946475</v>
+        <v>15476158495</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1222,13 +1222,13 @@
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G9" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>40129902900</v>
+        <v>42236023650</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14210</v>
+        <v>14170</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.33%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
         <v>111</v>
@@ -1340,13 +1340,13 @@
         <v>14770</v>
       </c>
       <c r="M10" t="n">
-        <v>14190</v>
+        <v>14150</v>
       </c>
       <c r="N10" t="n">
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>13864110755</v>
+        <v>14883095175</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26950</v>
+        <v>27100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.27%</t>
+          <t>'-4.75%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>29113004825</v>
+        <v>30058807825</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3185</v>
+        <v>3215</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-16.40%</t>
+          <t>'-15.62%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F12" t="n">
         <v>101</v>
       </c>
       <c r="G12" t="n">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>18432888339</v>
+        <v>18832571701</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국제 정세 악화 및 북한 관련 이슈로 인한 주가 급락 우려. 종목의 실질적인 가치에 대한 부정적 시각.</t>
+          <t>전쟁, 북한 관련 이슈로 인한 급락 가능성이 제기되며, 종목의 부진한 흐름과 동전주 전환에 대한 우려가 제기됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국제 정세', '주가 급락', '전쟁']</t>
+          <t>['전쟁', '북한', '급락']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261026_11.xlsx
+++ b/data/trending_integrated_20261026_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F2" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G2" t="n">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58626686055</v>
+        <v>58658240175</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2185</v>
+        <v>2160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.40%</t>
+          <t>'+11.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>54477875373</v>
+        <v>55135382238</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5910</v>
+        <v>5980</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.65%</t>
+          <t>'+8.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>34729455680</v>
+        <v>35784534905</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 내용으로, 실제 실체 없는 사기라는 의견과 함께 급락을 예상하는 의견이 혼재함.</t>
+          <t>정치 테마 관련 부정적 전망과 함께 개별 종목의 주가 하락 우려 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '실체', '급락']</t>
+          <t>['정치 테마', '주가 하락', '지지율']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1279000</v>
+        <v>1272000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'-0.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="G5" t="n">
-        <v>1519</v>
+        <v>1589</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -880,13 +880,13 @@
         <v>1315000</v>
       </c>
       <c r="M5" t="n">
-        <v>1272000</v>
+        <v>1270000</v>
       </c>
       <c r="N5" t="n">
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1619970979000</v>
+        <v>1658071322000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연금 관련 언급이 혼재하며, 주가 부양에 대한 기대와 함께 주가 하락 가능성에 대한 우려가 나타남.</t>
+          <t>정치적 요인과 증시 전반의 불안감 속에서 주가 반등 및 데이터센터 관련 전망 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치', '연금', '주가']</t>
+          <t>['정치 요인', '데이터센터', '주가 조작']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>212750</v>
+        <v>212500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'-1.39%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>457</v>
       </c>
       <c r="G6" t="n">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="H6" t="n">
         <v>46.11</v>
@@ -978,7 +978,7 @@
         <v>46.13</v>
       </c>
       <c r="O6" t="n">
-        <v>1212285027000</v>
+        <v>1226032174500</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치 관련 부정적인 언급과 함께 한국 증시에 대한 불만이 표출되며, 주식 시장 자체에 대한 회의적인 시각을 보임.</t>
+          <t>정부 정책 및 정치 이슈에 대한 불만과 함께 한국 증시의 부정적 전망 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['정치', '한국 증시', '회의론']</t>
+          <t>['한국 증시', '정부 정책', '외인 기관']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58900</v>
+        <v>58800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-1.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.49</v>
       </c>
       <c r="E7" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
-        <v>515</v>
+        <v>549</v>
       </c>
       <c r="H7" t="n">
         <v>40.39</v>
@@ -1070,7 +1070,7 @@
         <v>38.9</v>
       </c>
       <c r="O7" t="n">
-        <v>152096119950</v>
+        <v>155650919800</v>
       </c>
       <c r="P7" t="n">
         <v>67300</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외인 매수세 유입과 긍정적인 수급 동향을 바탕으로 주가 상승 기대감 표출. 중동 전쟁 등 외부 요인 언급.</t>
+          <t>기술적 분석 및 수급 동향 기반 긍정적 전망, 유동성 장세와 중동 전쟁 변수 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인 매수', '수급 동향', '상승 기대']</t>
+          <t>['기술적 분석', '수급 동향', '유동성 장세']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16440</v>
+        <v>16410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.32%</t>
+          <t>'-2.50%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>15476158495</v>
+        <v>15968924860</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57800</v>
+        <v>57700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F9" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G9" t="n">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>42236023650</v>
+        <v>43001875900</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정부 정책 및 증시 상황에 대한 불만과 함께 종목의 하락 추세에 대한 부정적 전망. 근거 없는 비난 다수 포함.</t>
+          <t>정부 정책 및 정치 이슈에 대한 불만과 함께 원전 및 반도체 시장 상황을 고려한 주가 하락 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정부 정책', '증시 상황', '하락 추세']</t>
+          <t>['정부 정책', '원전', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14170</v>
+        <v>14140</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.81%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1340,13 +1340,13 @@
         <v>14770</v>
       </c>
       <c r="M10" t="n">
-        <v>14150</v>
+        <v>14100</v>
       </c>
       <c r="N10" t="n">
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>14883095175</v>
+        <v>15741161490</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27100</v>
+        <v>27000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-5.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>30058807825</v>
+        <v>30688812475</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3215</v>
+        <v>3110</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-15.62%</t>
+          <t>'-18.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="F12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G12" t="n">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1524,13 +1524,13 @@
         <v>3555</v>
       </c>
       <c r="M12" t="n">
-        <v>3185</v>
+        <v>3080</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>18832571701</v>
+        <v>20153196382</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>전쟁, 북한 관련 이슈로 인한 급락 가능성이 제기되며, 종목의 부진한 흐름과 동전주 전환에 대한 우려가 제기됨.</t>
+          <t>북한 관련 지정학적 리스크와 전쟁 위기 고조 속 급락 가능성 및 종목의 부실함 경고.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['전쟁', '북한', '급락']</t>
+          <t>['지정학적 리스크', '전쟁 위기', '폭락']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261026_11.xlsx
+++ b/data/trending_integrated_20261026_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58658240175</v>
+        <v>58756075575</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2160</v>
+        <v>2185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.11%</t>
+          <t>'+12.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>55135382238</v>
+        <v>55803086695</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5980</v>
+        <v>5840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.93%</t>
+          <t>'+6.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>110</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>35784534905</v>
+        <v>36311591485</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마 관련 부정적 전망과 함께 개별 종목의 주가 하락 우려 제기.</t>
+          <t>정치 테마주 관련 허위 정보 유포 및 투자 주의 촉구. 부정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마', '주가 하락', '지지율']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1272000</v>
+        <v>1270000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.39%</t>
+          <t>'-0.55%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>471</v>
       </c>
       <c r="G5" t="n">
-        <v>1589</v>
+        <v>1636</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -880,13 +880,13 @@
         <v>1315000</v>
       </c>
       <c r="M5" t="n">
-        <v>1270000</v>
+        <v>1268000</v>
       </c>
       <c r="N5" t="n">
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1658071322000</v>
+        <v>1694423928500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 요인과 증시 전반의 불안감 속에서 주가 반등 및 데이터센터 관련 전망 언급.</t>
+          <t>정치적 불확실성 및 시장 전반의 부정적 영향 언급. 외인 매도세 지속 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치 요인', '데이터센터', '주가 조작']</t>
+          <t>['외인 매도', '정치 테마', '시장 영향']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>212500</v>
+        <v>212250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.39%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="G6" t="n">
-        <v>1373</v>
+        <v>1410</v>
       </c>
       <c r="H6" t="n">
         <v>46.11</v>
@@ -978,7 +978,7 @@
         <v>46.13</v>
       </c>
       <c r="O6" t="n">
-        <v>1226032174500</v>
+        <v>1241466157250</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정부 정책 및 정치 이슈에 대한 불만과 함께 한국 증시의 부정적 전망 제시.</t>
+          <t>정치적 이슈 및 정부 정책에 대한 부정적 언급. 외인 수급 부진 및 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['한국 증시', '정부 정책', '외인 기관']</t>
+          <t>['외인 수급', '정치 테마', '투자 심리']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58800</v>
+        <v>58600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.67%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.49</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="H7" t="n">
         <v>40.39</v>
@@ -1070,7 +1070,7 @@
         <v>38.9</v>
       </c>
       <c r="O7" t="n">
-        <v>155650919800</v>
+        <v>157942282000</v>
       </c>
       <c r="P7" t="n">
         <v>67300</v>
@@ -1130,13 +1130,13 @@
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>15968924860</v>
+        <v>16535785715</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57700</v>
+        <v>57600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>103</v>
       </c>
       <c r="G9" t="n">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>43001875900</v>
+        <v>44128190250</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14140</v>
+        <v>14110</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.81%</t>
+          <t>'-4.01%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>15741161490</v>
+        <v>16022627875</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27000</v>
+        <v>26900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.10%</t>
+          <t>'-5.45%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>30688812475</v>
+        <v>31305029400</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3110</v>
+        <v>3115</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-18.37%</t>
+          <t>'-18.24%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="F12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G12" t="n">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>20153196382</v>
+        <v>20741858778</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크와 전쟁 위기 고조 속 급락 가능성 및 종목의 부실함 경고.</t>
+          <t>지정학적 리스크 및 군사적 긴장 고조에 따른 급락. 단기적 변동성 확대 및 투자 심리 악화.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '전쟁 위기', '폭락']</t>
+          <t>['지정학적 리스크', '군사적 긴장', '단기 변동성']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261026_11.xlsx
+++ b/data/trending_integrated_20261026_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G2" t="n">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58756075575</v>
+        <v>58770457085</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와의 협력에 따른 주가 급등 전망. 공매도 상환 압박 언급.</t>
+          <t>공매도 쇼트 스퀴즈 기대감과 글로벌 AI 신약 밸류체인 합류. 연기금 순매수.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '협력', '공매도']</t>
+          <t>['AI', '신약', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2185</v>
+        <v>2165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.40%</t>
+          <t>'+11.37%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
         <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>55803086695</v>
+        <v>56048791135</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5840</v>
+        <v>5980</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.38%</t>
+          <t>'+8.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>36311591485</v>
+        <v>36761159100</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 허위 정보 유포 및 투자 주의 촉구. 부정적 전망.</t>
+          <t>정치 테마주에 대한 회의론과 급락 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치테마', '개미', '급락']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="G5" t="n">
-        <v>1636</v>
+        <v>1662</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1694423928500</v>
+        <v>1720358142500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 불확실성 및 시장 전반의 부정적 영향 언급. 외인 매도세 지속 및 주가 하락 우려.</t>
+          <t>주가 조작 의혹과 시장 상황에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외인 매도', '정치 테마', '시장 영향']</t>
+          <t>['주가조작', '레버리지', '외인']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="G6" t="n">
-        <v>1410</v>
+        <v>1444</v>
       </c>
       <c r="H6" t="n">
         <v>46.11</v>
@@ -978,7 +978,7 @@
         <v>46.13</v>
       </c>
       <c r="O6" t="n">
-        <v>1241466157250</v>
+        <v>1258467776250</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 정부 정책에 대한 부정적 언급. 외인 수급 부진 및 투자 심리 위축.</t>
+          <t>정부 정책에 대한 비판과 외국인 매도세 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인 수급', '정치 테마', '투자 심리']</t>
+          <t>['외인', '정부', '경제']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58600</v>
+        <v>58800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-1.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.49</v>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="H7" t="n">
         <v>40.39</v>
@@ -1070,7 +1070,7 @@
         <v>38.9</v>
       </c>
       <c r="O7" t="n">
-        <v>157942282000</v>
+        <v>160347559300</v>
       </c>
       <c r="P7" t="n">
         <v>67300</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기술적 분석 및 수급 동향 기반 긍정적 전망, 유동성 장세와 중동 전쟁 변수 언급.</t>
+          <t>공매도 세력에 대한 경고와 상승 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기술적 분석', '수급 동향', '유동성 장세']</t>
+          <t>['공매도', '수급', '자사주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16410</v>
+        <v>16360</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.50%</t>
+          <t>'-2.79%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1156,19 +1156,19 @@
         <v>16820</v>
       </c>
       <c r="M8" t="n">
-        <v>16400</v>
+        <v>16340</v>
       </c>
       <c r="N8" t="n">
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>16535785715</v>
+        <v>17978627095</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>16400</v>
+        <v>16340</v>
       </c>
       <c r="R8" t="n">
         <v>219000</v>
@@ -1222,13 +1222,13 @@
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F9" t="n">
         <v>103</v>
       </c>
       <c r="G9" t="n">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>44128190250</v>
+        <v>44925695800</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정부 정책 및 정치 이슈에 대한 불만과 함께 원전 및 반도체 시장 상황을 고려한 주가 하락 전망.</t>
+          <t>정부 정책 실패와 원전 사업 불확실성에 따른 급락 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정부 정책', '원전', '반도체']</t>
+          <t>['정부', '신용', '원전']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14110</v>
+        <v>14120</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.01%</t>
+          <t>'-3.95%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
         <v>112</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>16022627875</v>
+        <v>16296002095</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26900</v>
+        <v>26950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.45%</t>
+          <t>'-5.27%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>31305029400</v>
+        <v>31967251250</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="F12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G12" t="n">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>20741858778</v>
+        <v>21034596863</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>지정학적 리스크 및 군사적 긴장 고조에 따른 급락. 단기적 변동성 확대 및 투자 심리 악화.</t>
+          <t>지정학적 리스크 부각 속 급락 및 신용 위험 경고.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '군사적 긴장', '단기 변동성']</t>
+          <t>['북한', '전쟁', '신용']</t>
         </is>
       </c>
       <c r="X12" t="n">
